--- a/output/graficos_nacionales/plot_nacional_e_mat_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_mat_a_2019.xlsx
@@ -15589,7 +15589,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tasa de matrícula población de 0 a 24 años</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_e_mat_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_mat_a_2019.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -14124,7 +14124,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -15734,7 +15734,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -15780,7 +15780,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -15826,7 +15826,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_e_mat_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_mat_a_2019.xlsx
@@ -2134,7 +2134,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:35</t>
+    <t xml:space="preserve">2026-09-07 12:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_mat_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_mat_a_2019.xlsx
@@ -2134,7 +2134,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:48</t>
+    <t xml:space="preserve">2026-09-08 10:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
